--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-encounter.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-encounter.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$140</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4616" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5012" uniqueCount="591">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:49:50+00:00</t>
+    <t>2025-09-03T12:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -832,17 +832,10 @@
     <t>Encounter.participant</t>
   </si>
   <si>
-    <t>List of participants involved in the encounter</t>
+    <t>Liste des participants impliqués dans la rencontre</t>
   </si>
   <si>
     <t>The list of people responsible for providing the service.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:type.coding.code}
-</t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Event.performer</t>
@@ -927,34 +920,10 @@
     <t>ROL-4</t>
   </si>
   <si>
-    <t>Encounter.participant:author</t>
-  </si>
-  <si>
-    <t>author</t>
-  </si>
-  <si>
-    <t>Encounter.participant:author.id</t>
-  </si>
-  <si>
-    <t>Encounter.participant:author.extension</t>
-  </si>
-  <si>
-    <t>Encounter.participant:author.modifierExtension</t>
-  </si>
-  <si>
-    <t>Encounter.participant:author.type</t>
-  </si>
-  <si>
-    <t>Encounter.participant:author.type.id</t>
-  </si>
-  <si>
-    <t>Encounter.participant.type.id</t>
-  </si>
-  <si>
-    <t>Encounter.participant:author.type.extension</t>
-  </si>
-  <si>
-    <t>Encounter.participant.type.extension</t>
+    <t>Encounter.participant.individual.id</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -964,288 +933,17 @@
     <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
-    <t>Encounter.participant:author.type.coding</t>
-  </si>
-  <si>
-    <t>Encounter.participant.type.coding</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>Encounter.participant:author.type.coding.id</t>
-  </si>
-  <si>
-    <t>Encounter.participant.type.coding.id</t>
-  </si>
-  <si>
-    <t>Encounter.participant:author.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Encounter.participant.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Encounter.participant:author.type.coding.system</t>
-  </si>
-  <si>
-    <t>Encounter.participant.type.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ParticipationType-cisis</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>Encounter.participant:author.type.coding.version</t>
-  </si>
-  <si>
-    <t>Encounter.participant.type.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>Encounter.participant:author.type.coding.code</t>
-  </si>
-  <si>
-    <t>Encounter.participant.type.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>AUT</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>Encounter.participant:author.type.coding.display</t>
-  </si>
-  <si>
-    <t>Encounter.participant.type.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Author</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>Encounter.participant:author.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Encounter.participant.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
+    <t>open</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:executant</t>
+  </si>
+  <si>
+    <t>executant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension}
 </t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>Encounter.participant:author.type.text</t>
-  </si>
-  <si>
-    <t>Encounter.participant.type.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>Encounter.participant:author.period</t>
-  </si>
-  <si>
-    <t>Encounter.participant:author.individual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-related-person-document)
-</t>
-  </si>
-  <si>
-    <t>Encounter.participant:informant</t>
-  </si>
-  <si>
-    <t>informant</t>
-  </si>
-  <si>
-    <t>Encounter.participant:informant.id</t>
-  </si>
-  <si>
-    <t>Encounter.participant:informant.extension</t>
-  </si>
-  <si>
-    <t>Encounter.participant:informant.modifierExtension</t>
-  </si>
-  <si>
-    <t>Encounter.participant:informant.type</t>
-  </si>
-  <si>
-    <t>Encounter.participant:informant.type.id</t>
-  </si>
-  <si>
-    <t>Encounter.participant:informant.type.extension</t>
-  </si>
-  <si>
-    <t>Encounter.participant:informant.type.coding</t>
-  </si>
-  <si>
-    <t>Encounter.participant:informant.type.coding.id</t>
-  </si>
-  <si>
-    <t>Encounter.participant:informant.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Encounter.participant:informant.type.coding.system</t>
-  </si>
-  <si>
-    <t>Encounter.participant:informant.type.coding.version</t>
-  </si>
-  <si>
-    <t>Encounter.participant:informant.type.coding.code</t>
-  </si>
-  <si>
-    <t>INF</t>
-  </si>
-  <si>
-    <t>Encounter.participant:informant.type.coding.display</t>
-  </si>
-  <si>
-    <t>Informant</t>
-  </si>
-  <si>
-    <t>Encounter.participant:informant.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Encounter.participant:informant.type.text</t>
-  </si>
-  <si>
-    <t>Encounter.participant:informant.period</t>
-  </si>
-  <si>
-    <t>Encounter.participant:informant.individual</t>
-  </si>
-  <si>
-    <t>Encounter.participant:executant</t>
-  </si>
-  <si>
-    <t>executant</t>
   </si>
   <si>
     <t>Exécutant : 
@@ -1254,61 +952,365 @@
 Sinon : l'exécutant n'est pas obligatoire mais peut être renseigné</t>
   </si>
   <si>
-    <t>Encounter.participant:executant.id</t>
-  </si>
-  <si>
-    <t>Encounter.participant:executant.extension</t>
-  </si>
-  <si>
-    <t>Encounter.participant:executant.modifierExtension</t>
-  </si>
-  <si>
-    <t>Encounter.participant:executant.type</t>
-  </si>
-  <si>
-    <t>Encounter.participant:executant.type.id</t>
-  </si>
-  <si>
-    <t>Encounter.participant:executant.type.extension</t>
-  </si>
-  <si>
-    <t>Encounter.participant:executant.type.coding</t>
-  </si>
-  <si>
-    <t>Encounter.participant:executant.type.coding.id</t>
-  </si>
-  <si>
-    <t>Encounter.participant:executant.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Encounter.participant:executant.type.coding.system</t>
-  </si>
-  <si>
-    <t>Encounter.participant:executant.type.coding.version</t>
-  </si>
-  <si>
-    <t>Encounter.participant:executant.type.coding.code</t>
+    <t>Extension pour représenter un acteur impliqué dans le document avec son type et sa référence.</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:executant.id</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension.id</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:executant.extension</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension.extension</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:executant.extension:type</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:executant.extension:type.id</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension.extension.id</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:executant.extension:type.extension</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:executant.extension:type.url</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:executant.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>PRF</t>
   </si>
   <si>
-    <t>Encounter.participant:executant.type.coding.display</t>
-  </si>
-  <si>
-    <t>Performer</t>
-  </si>
-  <si>
-    <t>Encounter.participant:executant.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Encounter.participant:executant.type.text</t>
-  </si>
-  <si>
-    <t>Encounter.participant:executant.period</t>
-  </si>
-  <si>
-    <t>Encounter.participant:executant.individual</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-actor-type</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:executant.extension:typeCode</t>
+  </si>
+  <si>
+    <t>typeCode</t>
+  </si>
+  <si>
+    <t>Type de participation</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:executant.extension:typeCode.id</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:executant.extension:typeCode.extension</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:executant.extension:typeCode.url</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:executant.extension:typeCode.value[x]</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:executant.extension:reference</t>
+  </si>
+  <si>
+    <t>reference</t>
+  </si>
+  <si>
+    <t>Référence vers le rôle du praticien dans le document</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:executant.extension:reference.id</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:executant.extension:reference.extension</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:executant.extension:reference.url</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:executant.extension:reference.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|Device|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-device-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-organization-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-related-person-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-document)
+</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:executant.url</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension.url</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:executant.value[x]</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension.value[x]</t>
+  </si>
+  <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:author</t>
+  </si>
+  <si>
+    <t>author</t>
+  </si>
+  <si>
+    <t>Author</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:author.id</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:author.extension</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:author.extension:type</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:author.extension:type.id</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:author.extension:type.extension</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:author.extension:type.url</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:author.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>AUT</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:author.extension:typeCode</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:author.extension:typeCode.id</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:author.extension:typeCode.extension</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:author.extension:typeCode.url</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:author.extension:typeCode.value[x]</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:author.extension:reference</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:author.extension:reference.id</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:author.extension:reference.extension</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:author.extension:reference.url</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:author.extension:reference.value[x]</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:author.url</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:author.value[x]</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:informant</t>
+  </si>
+  <si>
+    <t>informant</t>
+  </si>
+  <si>
+    <t>Informant</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:informant.id</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:informant.extension</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:informant.extension:type</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:informant.extension:type.id</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:informant.extension:type.extension</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:informant.extension:type.url</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:informant.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>INF</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:informant.extension:typeCode</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:informant.extension:typeCode.id</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:informant.extension:typeCode.extension</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:informant.extension:typeCode.url</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:informant.extension:typeCode.value[x]</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:informant.extension:reference</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:informant.extension:reference.id</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:informant.extension:reference.extension</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:informant.extension:reference.url</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:informant.extension:reference.value[x]</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:informant.url</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.extension:informant.value[x]</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.reference</t>
+  </si>
+  <si>
+    <t>Literal reference, Relative, internal or absolute URL</t>
+  </si>
+  <si>
+    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
+  </si>
+  <si>
+    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
+  </si>
+  <si>
+    <t>Reference.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref-1
+</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.type</t>
+  </si>
+  <si>
+    <t>Type the reference refers to (e.g. "Patient")</t>
+  </si>
+  <si>
+    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
+The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
+  </si>
+  <si>
+    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+  </si>
+  <si>
+    <t>Reference.type</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.identifier</t>
+  </si>
+  <si>
+    <t>Logical reference, when literal reference is not known</t>
+  </si>
+  <si>
+    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
+  </si>
+  <si>
+    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
+When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
+Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
+Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
+  </si>
+  <si>
+    <t>Reference.identifier</t>
+  </si>
+  <si>
+    <t>.identifier</t>
+  </si>
+  <si>
+    <t>Encounter.participant.individual.display</t>
+  </si>
+  <si>
+    <t>Text alternative for the resource</t>
+  </si>
+  <si>
+    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
+  </si>
+  <si>
+    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>Reference.display</t>
   </si>
   <si>
     <t>Encounter.appointment</t>
@@ -2169,11 +2171,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN128"/>
+  <dimension ref="A1:AN140"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="46.91796875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="39.16015625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="67.2109375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="50.66015625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -2182,7 +2184,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="162.5078125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2197,9 +2199,9 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="64.00390625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="58.7578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.4296875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.2734375" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
@@ -5804,14 +5806,16 @@
         <v>80</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="AC32" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>259</v>
@@ -5829,24 +5833,24 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>266</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5955,10 +5959,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6069,10 +6073,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6185,10 +6189,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6214,13 +6218,13 @@
         <v>212</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6249,11 +6253,11 @@
         <v>193</v>
       </c>
       <c r="Y36" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="Z36" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="Z36" t="s" s="2">
-        <v>274</v>
-      </c>
       <c r="AA36" t="s" s="2">
         <v>80</v>
       </c>
@@ -6270,7 +6274,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6285,24 +6289,24 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>277</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6328,10 +6332,10 @@
         <v>186</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6382,7 +6386,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6400,21 +6404,21 @@
         <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6437,13 +6441,13 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="L38" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6494,7 +6498,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6509,28 +6513,26 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>290</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>80</v>
       </c>
@@ -6539,7 +6541,7 @@
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>80</v>
@@ -6548,16 +6550,16 @@
         <v>80</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>260</v>
+        <v>172</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>261</v>
+        <v>173</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6608,50 +6610,50 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>259</v>
+        <v>174</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>264</v>
+        <v>80</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>265</v>
+        <v>169</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>266</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>267</v>
+        <v>290</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>80</v>
@@ -6663,15 +6665,17 @@
         <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>80</v>
@@ -6708,31 +6712,31 @@
         <v>80</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>80</v>
+        <v>291</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>80</v>
+        <v>292</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>80</v>
+        <v>293</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>80</v>
@@ -6752,11 +6756,13 @@
         <v>294</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="C41" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="D41" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6775,17 +6781,15 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>134</v>
+        <v>296</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>135</v>
+        <v>297</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -6852,7 +6856,7 @@
         <v>80</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>169</v>
+        <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>80</v>
@@ -6863,46 +6867,42 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>269</v>
+        <v>300</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>80</v>
       </c>
@@ -6950,25 +6950,25 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>80</v>
@@ -6979,10 +6979,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>270</v>
+        <v>302</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>78</v>
+        <v>303</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>79</v>
@@ -7002,20 +7002,18 @@
         <v>80</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>212</v>
+        <v>134</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>271</v>
+        <v>304</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>80</v>
@@ -7040,31 +7038,31 @@
         <v>80</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>193</v>
+        <v>80</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>272</v>
+        <v>80</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>274</v>
+        <v>80</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>80</v>
+        <v>291</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>80</v>
+        <v>292</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>80</v>
+        <v>293</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>270</v>
+        <v>177</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7076,35 +7074,37 @@
         <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>275</v>
+        <v>80</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>276</v>
+        <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>277</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="D44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>88</v>
@@ -7119,13 +7119,13 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>172</v>
+        <v>304</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>173</v>
+        <v>305</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7176,25 +7176,25 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>169</v>
+        <v>80</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>80</v>
@@ -7205,21 +7205,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>80</v>
@@ -7231,17 +7231,15 @@
         <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>80</v>
@@ -7278,31 +7276,31 @@
         <v>80</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>301</v>
+        <v>80</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>302</v>
+        <v>80</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>80</v>
@@ -7319,10 +7317,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7333,7 +7331,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>80</v>
@@ -7342,23 +7340,19 @@
         <v>80</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>190</v>
+        <v>134</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="M46" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>308</v>
-      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>80</v>
       </c>
@@ -7394,19 +7388,19 @@
         <v>80</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>80</v>
+        <v>291</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>80</v>
+        <v>292</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>80</v>
+        <v>293</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>309</v>
+        <v>177</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7418,19 +7412,19 @@
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>310</v>
+        <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>311</v>
+        <v>80</v>
       </c>
     </row>
     <row r="47" hidden="true">
@@ -7446,7 +7440,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>88</v>
@@ -7461,22 +7455,24 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>171</v>
+        <v>102</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>172</v>
+        <v>314</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>316</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>80</v>
+        <v>307</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>80</v>
@@ -7518,10 +7514,10 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>174</v>
+        <v>317</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>88</v>
@@ -7536,7 +7532,7 @@
         <v>80</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>80</v>
@@ -7547,21 +7543,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>80</v>
@@ -7573,24 +7569,22 @@
         <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>135</v>
+        <v>320</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>80</v>
+        <v>322</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>80</v>
@@ -7608,49 +7602,47 @@
         <v>80</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>80</v>
+        <v>323</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>301</v>
+        <v>80</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>302</v>
+        <v>80</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>177</v>
+        <v>324</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>80</v>
@@ -7661,12 +7653,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="C49" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="D49" t="s" s="2">
         <v>80</v>
       </c>
@@ -7684,23 +7678,19 @@
         <v>80</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>80</v>
       </c>
@@ -7724,11 +7714,13 @@
         <v>80</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y49" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z49" t="s" s="2">
-        <v>322</v>
+        <v>80</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>80</v>
@@ -7746,39 +7738,39 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>323</v>
+        <v>177</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>324</v>
+        <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>325</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>327</v>
+        <v>309</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7798,20 +7790,18 @@
         <v>80</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
         <v>171</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>328</v>
+        <v>172</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -7860,7 +7850,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>331</v>
+        <v>174</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7872,27 +7862,27 @@
         <v>80</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>332</v>
+        <v>169</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>333</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7900,10 +7890,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>80</v>
@@ -7912,21 +7902,19 @@
         <v>80</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>336</v>
+        <v>304</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>337</v>
+        <v>305</v>
       </c>
       <c r="N51" s="2"/>
-      <c r="O51" t="s" s="2">
-        <v>338</v>
-      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>80</v>
       </c>
@@ -7935,7 +7923,7 @@
         <v>80</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>339</v>
+        <v>80</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>80</v>
@@ -7962,51 +7950,51 @@
         <v>80</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>80</v>
+        <v>291</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>80</v>
+        <v>292</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>80</v>
+        <v>293</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>340</v>
+        <v>177</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>341</v>
+        <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>342</v>
+        <v>80</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>344</v>
+        <v>313</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8014,7 +8002,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>88</v>
@@ -8026,30 +8014,30 @@
         <v>80</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>171</v>
+        <v>102</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>345</v>
+        <v>314</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>80</v>
+        <v>326</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>348</v>
+        <v>80</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>80</v>
@@ -8088,10 +8076,10 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>349</v>
+        <v>317</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>88</v>
@@ -8100,27 +8088,27 @@
         <v>80</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>350</v>
+        <v>131</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>351</v>
+        <v>80</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>352</v>
+        <v>331</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>353</v>
+        <v>319</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8140,23 +8128,19 @@
         <v>80</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>354</v>
+        <v>212</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>355</v>
+        <v>320</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>358</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>80</v>
       </c>
@@ -8204,7 +8188,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>359</v>
+        <v>324</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8222,29 +8206,31 @@
         <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>360</v>
+        <v>131</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>361</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>362</v>
+        <v>332</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="C54" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="D54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>88</v>
@@ -8256,23 +8242,19 @@
         <v>80</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>364</v>
+        <v>334</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>80</v>
       </c>
@@ -8320,39 +8302,39 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>368</v>
+        <v>177</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>369</v>
+        <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>370</v>
+        <v>80</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>371</v>
+        <v>335</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>278</v>
+        <v>309</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8375,13 +8357,13 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>279</v>
+        <v>172</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>280</v>
+        <v>173</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8432,7 +8414,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>278</v>
+        <v>174</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8444,27 +8426,27 @@
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>281</v>
+        <v>169</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>282</v>
+        <v>80</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>372</v>
+        <v>336</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>283</v>
+        <v>311</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8475,7 +8457,7 @@
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>80</v>
@@ -8484,16 +8466,16 @@
         <v>80</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>373</v>
+        <v>134</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8532,64 +8514,62 @@
         <v>80</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>80</v>
+        <v>291</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>80</v>
+        <v>292</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>80</v>
+        <v>293</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>283</v>
+        <v>177</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>287</v>
+        <v>80</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>288</v>
+        <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>289</v>
+        <v>80</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>290</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>374</v>
+        <v>337</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>80</v>
@@ -8598,25 +8578,27 @@
         <v>80</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>165</v>
+        <v>102</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>260</v>
+        <v>314</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>316</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
-        <v>80</v>
+        <v>333</v>
       </c>
       <c r="S57" t="s" s="2">
         <v>80</v>
@@ -8658,39 +8640,39 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>259</v>
+        <v>317</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>264</v>
+        <v>80</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>265</v>
+        <v>131</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>266</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>376</v>
+        <v>338</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>267</v>
+        <v>319</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8713,13 +8695,13 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>171</v>
+        <v>339</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>172</v>
+        <v>320</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>173</v>
+        <v>321</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8770,7 +8752,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>174</v>
+        <v>324</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8782,13 +8764,13 @@
         <v>80</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>80</v>
@@ -8799,21 +8781,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>377</v>
+        <v>340</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>268</v>
+        <v>341</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>80</v>
@@ -8825,16 +8807,16 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>135</v>
+        <v>314</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>176</v>
+        <v>315</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>137</v>
+        <v>316</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8842,7 +8824,7 @@
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>80</v>
+        <v>342</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>80</v>
@@ -8884,25 +8866,25 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>177</v>
+        <v>317</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>80</v>
@@ -8913,46 +8895,42 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>378</v>
+        <v>343</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>269</v>
+        <v>344</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>134</v>
+        <v>345</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>180</v>
+        <v>320</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>80</v>
       </c>
@@ -9000,19 +8978,19 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>182</v>
+        <v>324</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>80</v>
@@ -9029,12 +9007,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>379</v>
+        <v>346</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="C61" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="D61" t="s" s="2">
         <v>80</v>
       </c>
@@ -9052,20 +9032,18 @@
         <v>80</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>212</v>
+        <v>296</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>271</v>
+        <v>348</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>80</v>
@@ -9090,13 +9068,13 @@
         <v>80</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>193</v>
+        <v>80</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>272</v>
+        <v>80</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>274</v>
+        <v>80</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>80</v>
@@ -9114,7 +9092,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>270</v>
+        <v>177</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9126,27 +9104,27 @@
         <v>80</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>275</v>
+        <v>80</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>276</v>
+        <v>80</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>277</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>380</v>
+        <v>349</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9255,18 +9233,18 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>381</v>
+        <v>350</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>78</v>
+        <v>303</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>79</v>
@@ -9284,14 +9262,12 @@
         <v>134</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>135</v>
+        <v>304</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>80</v>
@@ -9328,16 +9304,16 @@
         <v>80</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>177</v>
@@ -9358,7 +9334,7 @@
         <v>80</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>169</v>
+        <v>80</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>80</v>
@@ -9369,21 +9345,23 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>382</v>
+        <v>351</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="C64" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="D64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>80</v>
@@ -9392,23 +9370,19 @@
         <v>80</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>190</v>
+        <v>134</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="M64" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>308</v>
-      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>80</v>
       </c>
@@ -9456,7 +9430,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>309</v>
+        <v>177</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9468,27 +9442,27 @@
         <v>80</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>310</v>
+        <v>80</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>311</v>
+        <v>80</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>383</v>
+        <v>352</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9597,21 +9571,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>384</v>
+        <v>353</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>80</v>
@@ -9626,14 +9600,12 @@
         <v>134</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>135</v>
+        <v>304</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>80</v>
@@ -9670,16 +9642,16 @@
         <v>80</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="AF66" t="s" s="2">
         <v>177</v>
@@ -9700,7 +9672,7 @@
         <v>80</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>169</v>
+        <v>80</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>80</v>
@@ -9711,10 +9683,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>385</v>
+        <v>354</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9722,7 +9694,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>88</v>
@@ -9734,29 +9706,27 @@
         <v>80</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K67" t="s" s="2">
         <v>102</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>80</v>
+        <v>307</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>80</v>
@@ -9774,11 +9744,13 @@
         <v>80</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y67" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z67" t="s" s="2">
-        <v>322</v>
+        <v>80</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>80</v>
@@ -9796,10 +9768,10 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>88</v>
@@ -9808,27 +9780,27 @@
         <v>80</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>324</v>
+        <v>131</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>325</v>
+        <v>80</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>386</v>
+        <v>355</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9848,27 +9820,25 @@
         <v>80</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>171</v>
+        <v>108</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" t="s" s="2">
-        <v>80</v>
+        <v>356</v>
       </c>
       <c r="S68" t="s" s="2">
         <v>80</v>
@@ -9886,13 +9856,11 @@
         <v>80</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
-        <v>80</v>
+        <v>323</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>80</v>
@@ -9910,7 +9878,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9928,29 +9896,31 @@
         <v>80</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>332</v>
+        <v>131</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>333</v>
+        <v>80</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>387</v>
+        <v>357</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="C69" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="D69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>88</v>
@@ -9962,21 +9932,19 @@
         <v>80</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>337</v>
+        <v>305</v>
       </c>
       <c r="N69" s="2"/>
-      <c r="O69" t="s" s="2">
-        <v>338</v>
-      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>80</v>
       </c>
@@ -9985,7 +9953,7 @@
         <v>80</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>388</v>
+        <v>80</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>80</v>
@@ -10024,39 +9992,39 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>340</v>
+        <v>177</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>341</v>
+        <v>80</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>342</v>
+        <v>80</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>389</v>
+        <v>358</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>344</v>
+        <v>309</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10076,21 +10044,19 @@
         <v>80</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K70" t="s" s="2">
         <v>171</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>345</v>
+        <v>172</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>346</v>
+        <v>173</v>
       </c>
       <c r="N70" s="2"/>
-      <c r="O70" t="s" s="2">
-        <v>347</v>
-      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>80</v>
       </c>
@@ -10099,7 +10065,7 @@
         <v>80</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>390</v>
+        <v>80</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>80</v>
@@ -10138,7 +10104,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>349</v>
+        <v>174</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10150,27 +10116,27 @@
         <v>80</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>350</v>
+        <v>169</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>351</v>
+        <v>80</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>391</v>
+        <v>359</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>353</v>
+        <v>311</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10181,7 +10147,7 @@
         <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>80</v>
@@ -10190,23 +10156,19 @@
         <v>80</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>354</v>
+        <v>134</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>355</v>
+        <v>304</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>358</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>80</v>
       </c>
@@ -10242,51 +10204,51 @@
         <v>80</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>80</v>
+        <v>291</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>80</v>
+        <v>292</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>80</v>
+        <v>293</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>359</v>
+        <v>177</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>360</v>
+        <v>80</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>361</v>
+        <v>80</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>392</v>
+        <v>360</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>363</v>
+        <v>313</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10294,7 +10256,7 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>88</v>
@@ -10306,29 +10268,27 @@
         <v>80</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>171</v>
+        <v>102</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>364</v>
+        <v>314</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>365</v>
+        <v>315</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" t="s" s="2">
-        <v>80</v>
+        <v>326</v>
       </c>
       <c r="S72" t="s" s="2">
         <v>80</v>
@@ -10370,10 +10330,10 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>368</v>
+        <v>317</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>88</v>
@@ -10382,27 +10342,27 @@
         <v>80</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>369</v>
+        <v>131</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>370</v>
+        <v>80</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>393</v>
+        <v>361</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>278</v>
+        <v>319</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10425,13 +10385,13 @@
         <v>80</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>186</v>
+        <v>212</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>279</v>
+        <v>320</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>280</v>
+        <v>321</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10482,7 +10442,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>278</v>
+        <v>324</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10500,29 +10460,31 @@
         <v>80</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>281</v>
+        <v>131</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>282</v>
+        <v>80</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>394</v>
+        <v>362</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="C74" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="C74" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="D74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>88</v>
@@ -10534,16 +10496,16 @@
         <v>80</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>373</v>
+        <v>134</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>285</v>
+        <v>334</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10594,43 +10556,41 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>283</v>
+        <v>177</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>287</v>
+        <v>80</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>288</v>
+        <v>80</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>289</v>
+        <v>80</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>290</v>
+        <v>80</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>395</v>
+        <v>363</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="C75" t="s" s="2">
-        <v>396</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>80</v>
       </c>
@@ -10639,7 +10599,7 @@
         <v>78</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>80</v>
@@ -10648,16 +10608,16 @@
         <v>80</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>397</v>
+        <v>172</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>261</v>
+        <v>173</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10708,39 +10668,39 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>259</v>
+        <v>174</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>264</v>
+        <v>80</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>265</v>
+        <v>169</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>266</v>
+        <v>80</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>398</v>
+        <v>364</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>267</v>
+        <v>311</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10751,7 +10711,7 @@
         <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>80</v>
@@ -10763,13 +10723,13 @@
         <v>80</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>172</v>
+        <v>304</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>173</v>
+        <v>305</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10808,37 +10768,37 @@
         <v>80</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>80</v>
+        <v>291</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>80</v>
+        <v>292</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>80</v>
+        <v>293</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>169</v>
+        <v>80</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>80</v>
@@ -10849,21 +10809,21 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>399</v>
+        <v>365</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>268</v>
+        <v>313</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>80</v>
@@ -10875,16 +10835,16 @@
         <v>80</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>135</v>
+        <v>314</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>176</v>
+        <v>315</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>137</v>
+        <v>316</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10892,7 +10852,7 @@
       </c>
       <c r="Q77" s="2"/>
       <c r="R77" t="s" s="2">
-        <v>80</v>
+        <v>333</v>
       </c>
       <c r="S77" t="s" s="2">
         <v>80</v>
@@ -10934,25 +10894,25 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>177</v>
+        <v>317</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>80</v>
@@ -10963,46 +10923,42 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>400</v>
+        <v>366</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>269</v>
+        <v>319</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>134</v>
+        <v>339</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>180</v>
+        <v>320</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>80</v>
       </c>
@@ -11050,19 +11006,19 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>182</v>
+        <v>324</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>80</v>
@@ -11079,10 +11035,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>401</v>
+        <v>367</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>270</v>
+        <v>341</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11090,10 +11046,10 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>80</v>
@@ -11102,19 +11058,19 @@
         <v>80</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>212</v>
+        <v>102</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>271</v>
+        <v>314</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>272</v>
+        <v>315</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>273</v>
+        <v>316</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11122,7 +11078,7 @@
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
-        <v>80</v>
+        <v>342</v>
       </c>
       <c r="S79" t="s" s="2">
         <v>80</v>
@@ -11140,13 +11096,13 @@
         <v>80</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>193</v>
+        <v>80</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>272</v>
+        <v>80</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>274</v>
+        <v>80</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>80</v>
@@ -11164,39 +11120,39 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>270</v>
+        <v>317</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>275</v>
+        <v>80</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>276</v>
+        <v>131</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>277</v>
+        <v>80</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>402</v>
+        <v>368</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11207,7 +11163,7 @@
         <v>78</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>80</v>
@@ -11219,13 +11175,13 @@
         <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>171</v>
+        <v>345</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>172</v>
+        <v>320</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>173</v>
+        <v>321</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11276,7 +11232,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>174</v>
+        <v>324</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11288,13 +11244,13 @@
         <v>80</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>80</v>
@@ -11305,14 +11261,16 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>403</v>
+        <v>369</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="C81" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="C81" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="D81" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11331,17 +11289,15 @@
         <v>80</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>134</v>
+        <v>296</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>135</v>
+        <v>371</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>80</v>
@@ -11378,16 +11334,16 @@
         <v>80</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>301</v>
+        <v>80</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>302</v>
+        <v>80</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
         <v>177</v>
@@ -11408,7 +11364,7 @@
         <v>80</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>169</v>
+        <v>80</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>80</v>
@@ -11419,10 +11375,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>404</v>
+        <v>372</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11433,7 +11389,7 @@
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>80</v>
@@ -11442,23 +11398,19 @@
         <v>80</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>305</v>
+        <v>172</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>80</v>
       </c>
@@ -11506,39 +11458,39 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>309</v>
+        <v>174</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>310</v>
+        <v>169</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>311</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>405</v>
+        <v>373</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11546,10 +11498,10 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>78</v>
+        <v>303</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>80</v>
@@ -11561,13 +11513,13 @@
         <v>80</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>172</v>
+        <v>304</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>173</v>
+        <v>305</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11606,37 +11558,37 @@
         <v>80</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>80</v>
+        <v>291</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>80</v>
+        <v>292</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>80</v>
+        <v>293</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>169</v>
+        <v>80</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>80</v>
@@ -11647,21 +11599,23 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>406</v>
+        <v>374</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="C84" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="C84" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="D84" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>80</v>
@@ -11676,14 +11630,12 @@
         <v>134</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>135</v>
+        <v>304</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>80</v>
@@ -11720,16 +11672,16 @@
         <v>80</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>301</v>
+        <v>80</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>302</v>
+        <v>80</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
         <v>177</v>
@@ -11750,7 +11702,7 @@
         <v>80</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>169</v>
+        <v>80</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>80</v>
@@ -11761,10 +11713,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>407</v>
+        <v>375</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11784,23 +11736,19 @@
         <v>80</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>102</v>
+        <v>171</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>318</v>
+        <v>172</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>80</v>
       </c>
@@ -11824,11 +11772,13 @@
         <v>80</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y85" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z85" t="s" s="2">
-        <v>322</v>
+        <v>80</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>80</v>
@@ -11846,7 +11796,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>323</v>
+        <v>174</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11858,27 +11808,27 @@
         <v>80</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>324</v>
+        <v>169</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>325</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>408</v>
+        <v>376</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11889,7 +11839,7 @@
         <v>78</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>80</v>
@@ -11898,20 +11848,18 @@
         <v>80</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>328</v>
+        <v>304</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>80</v>
@@ -11948,51 +11896,51 @@
         <v>80</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>80</v>
+        <v>291</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>80</v>
+        <v>292</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>80</v>
+        <v>293</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>331</v>
+        <v>177</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>332</v>
+        <v>80</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>333</v>
+        <v>80</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>409</v>
+        <v>377</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12012,30 +11960,30 @@
         <v>80</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>336</v>
+        <v>314</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q87" s="2"/>
       <c r="R87" t="s" s="2">
-        <v>80</v>
+        <v>307</v>
       </c>
       <c r="S87" t="s" s="2">
-        <v>410</v>
+        <v>80</v>
       </c>
       <c r="T87" t="s" s="2">
         <v>80</v>
@@ -12074,10 +12022,10 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>340</v>
+        <v>317</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>88</v>
@@ -12086,27 +12034,27 @@
         <v>80</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>341</v>
+        <v>131</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>342</v>
+        <v>80</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>411</v>
+        <v>378</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>344</v>
+        <v>319</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12126,30 +12074,28 @@
         <v>80</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>171</v>
+        <v>108</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>345</v>
+        <v>320</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>346</v>
+        <v>321</v>
       </c>
       <c r="N88" s="2"/>
-      <c r="O88" t="s" s="2">
-        <v>347</v>
-      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q88" s="2"/>
       <c r="R88" t="s" s="2">
-        <v>80</v>
+        <v>379</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>412</v>
+        <v>80</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>80</v>
@@ -12164,13 +12110,11 @@
         <v>80</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>80</v>
+        <v>323</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>80</v>
@@ -12188,7 +12132,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>349</v>
+        <v>324</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12206,23 +12150,25 @@
         <v>80</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>350</v>
+        <v>131</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>351</v>
+        <v>80</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>413</v>
+        <v>380</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="C89" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="C89" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="D89" t="s" s="2">
         <v>80</v>
       </c>
@@ -12240,23 +12186,19 @@
         <v>80</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>354</v>
+        <v>134</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>355</v>
+        <v>327</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>358</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>80</v>
       </c>
@@ -12304,39 +12246,39 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>359</v>
+        <v>177</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>360</v>
+        <v>80</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>361</v>
+        <v>80</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>414</v>
+        <v>381</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>363</v>
+        <v>309</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12356,23 +12298,19 @@
         <v>80</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K90" t="s" s="2">
         <v>171</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>364</v>
+        <v>172</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>80</v>
       </c>
@@ -12420,7 +12358,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>368</v>
+        <v>174</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12432,27 +12370,27 @@
         <v>80</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>369</v>
+        <v>169</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>370</v>
+        <v>80</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>415</v>
+        <v>382</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>278</v>
+        <v>311</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12463,7 +12401,7 @@
         <v>78</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>80</v>
@@ -12475,13 +12413,13 @@
         <v>80</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>186</v>
+        <v>134</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>279</v>
+        <v>304</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12520,51 +12458,51 @@
         <v>80</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>80</v>
+        <v>291</v>
       </c>
       <c r="AC91" t="s" s="2">
-        <v>80</v>
+        <v>292</v>
       </c>
       <c r="AD91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>80</v>
+        <v>293</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>278</v>
+        <v>177</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>281</v>
+        <v>80</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>282</v>
+        <v>80</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>416</v>
+        <v>383</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12572,7 +12510,7 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>88</v>
@@ -12584,25 +12522,27 @@
         <v>80</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>373</v>
+        <v>102</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N92" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>316</v>
+      </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>80</v>
+        <v>326</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>80</v>
@@ -12644,10 +12584,10 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>283</v>
+        <v>317</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>88</v>
@@ -12656,27 +12596,27 @@
         <v>80</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>287</v>
+        <v>80</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>288</v>
+        <v>131</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>289</v>
+        <v>80</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>290</v>
+        <v>80</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>417</v>
+        <v>384</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>417</v>
+        <v>319</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12687,7 +12627,7 @@
         <v>78</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>80</v>
@@ -12696,16 +12636,16 @@
         <v>80</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>418</v>
+        <v>212</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>419</v>
+        <v>320</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>420</v>
+        <v>321</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -12756,13 +12696,13 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>417</v>
+        <v>324</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>80</v>
@@ -12771,38 +12711,40 @@
         <v>100</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>257</v>
+        <v>80</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>421</v>
+        <v>131</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>422</v>
+        <v>80</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>423</v>
+        <v>385</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="C94" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="C94" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="D94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G94" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>80</v>
@@ -12811,17 +12753,15 @@
         <v>80</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>186</v>
+        <v>134</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>424</v>
+        <v>334</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>426</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>80</v>
@@ -12870,39 +12810,39 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>423</v>
+        <v>177</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>427</v>
+        <v>80</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>428</v>
+        <v>80</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>429</v>
+        <v>80</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>430</v>
+        <v>80</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>431</v>
+        <v>386</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>431</v>
+        <v>309</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12925,17 +12865,15 @@
         <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>432</v>
+        <v>171</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>433</v>
+        <v>172</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>435</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>80</v>
@@ -12984,7 +12922,7 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>431</v>
+        <v>174</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -12996,38 +12934,38 @@
         <v>80</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>427</v>
+        <v>80</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>436</v>
+        <v>169</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>437</v>
+        <v>80</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>438</v>
+        <v>387</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>438</v>
+        <v>311</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>439</v>
+        <v>80</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>80</v>
@@ -13036,20 +12974,18 @@
         <v>80</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>212</v>
+        <v>134</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>440</v>
+        <v>304</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>442</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>80</v>
@@ -13074,31 +13010,31 @@
         <v>80</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>443</v>
+        <v>80</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>444</v>
+        <v>80</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>80</v>
+        <v>291</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>80</v>
+        <v>292</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>80</v>
+        <v>293</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>438</v>
+        <v>177</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13110,38 +13046,38 @@
         <v>80</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>445</v>
+        <v>80</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>446</v>
+        <v>80</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>447</v>
+        <v>80</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>448</v>
+        <v>80</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>449</v>
+        <v>388</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>449</v>
+        <v>313</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>439</v>
+        <v>80</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>80</v>
@@ -13150,19 +13086,19 @@
         <v>80</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>450</v>
+        <v>102</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>451</v>
+        <v>314</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>441</v>
+        <v>315</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>442</v>
+        <v>316</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13170,7 +13106,7 @@
       </c>
       <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
-        <v>80</v>
+        <v>333</v>
       </c>
       <c r="S97" t="s" s="2">
         <v>80</v>
@@ -13212,39 +13148,39 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>449</v>
+        <v>317</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>445</v>
+        <v>80</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>446</v>
+        <v>131</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>447</v>
+        <v>80</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>448</v>
+        <v>80</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>452</v>
+        <v>389</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>452</v>
+        <v>319</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13255,7 +13191,7 @@
         <v>78</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>80</v>
@@ -13264,16 +13200,16 @@
         <v>80</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>165</v>
+        <v>339</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>453</v>
+        <v>320</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>454</v>
+        <v>321</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13324,13 +13260,13 @@
         <v>80</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>452</v>
+        <v>324</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>80</v>
@@ -13342,7 +13278,7 @@
         <v>80</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>455</v>
+        <v>131</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>80</v>
@@ -13353,10 +13289,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>456</v>
+        <v>390</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>456</v>
+        <v>341</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13364,7 +13300,7 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>88</v>
@@ -13379,22 +13315,24 @@
         <v>80</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>171</v>
+        <v>102</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>172</v>
+        <v>314</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N99" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>316</v>
+      </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>80</v>
+        <v>342</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>80</v>
@@ -13436,10 +13374,10 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>174</v>
+        <v>317</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>88</v>
@@ -13454,7 +13392,7 @@
         <v>80</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>80</v>
@@ -13465,21 +13403,21 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>457</v>
+        <v>391</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>457</v>
+        <v>344</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>80</v>
@@ -13491,17 +13429,15 @@
         <v>80</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>134</v>
+        <v>345</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>135</v>
+        <v>320</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>80</v>
@@ -13550,25 +13486,25 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>177</v>
+        <v>324</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>80</v>
@@ -13579,46 +13515,44 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>458</v>
+        <v>392</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>458</v>
+        <v>392</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J101" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>180</v>
+        <v>393</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>181</v>
+        <v>394</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>80</v>
       </c>
@@ -13666,19 +13600,19 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>182</v>
+        <v>396</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>80</v>
+        <v>397</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>80</v>
@@ -13695,18 +13629,18 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>459</v>
+        <v>398</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>459</v>
+        <v>398</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>460</v>
+        <v>80</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>88</v>
@@ -13721,16 +13655,16 @@
         <v>89</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>461</v>
+        <v>102</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>462</v>
+        <v>399</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>463</v>
+        <v>400</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>442</v>
+        <v>401</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -13756,13 +13690,13 @@
         <v>80</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>80</v>
+        <v>193</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>80</v>
+        <v>402</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>80</v>
+        <v>403</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>80</v>
@@ -13780,10 +13714,10 @@
         <v>80</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>459</v>
+        <v>404</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>88</v>
@@ -13795,24 +13729,24 @@
         <v>100</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>464</v>
+        <v>80</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>465</v>
+        <v>131</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>447</v>
+        <v>80</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>466</v>
+        <v>80</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>467</v>
+        <v>405</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>467</v>
+        <v>405</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13832,18 +13766,20 @@
         <v>80</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>212</v>
+        <v>146</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>468</v>
+        <v>406</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>407</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>408</v>
+      </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>80</v>
@@ -13868,13 +13804,13 @@
         <v>80</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>470</v>
+        <v>80</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>471</v>
+        <v>80</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>80</v>
@@ -13892,7 +13828,7 @@
         <v>80</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>467</v>
+        <v>409</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -13910,7 +13846,7 @@
         <v>80</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>169</v>
+        <v>410</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>80</v>
@@ -13921,10 +13857,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>472</v>
+        <v>411</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>472</v>
+        <v>411</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13944,18 +13880,20 @@
         <v>80</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>473</v>
+        <v>171</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>474</v>
+        <v>412</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="N104" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>80</v>
@@ -14004,7 +13942,7 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>472</v>
+        <v>415</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14022,7 +13960,7 @@
         <v>80</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>476</v>
+        <v>131</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>80</v>
@@ -14033,10 +13971,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>477</v>
+        <v>416</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>477</v>
+        <v>416</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14056,20 +13994,18 @@
         <v>80</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>478</v>
+        <v>417</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>479</v>
+        <v>418</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="N105" s="2"/>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>80</v>
@@ -14118,7 +14054,7 @@
         <v>80</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>477</v>
+        <v>416</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -14133,24 +14069,24 @@
         <v>100</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>80</v>
+        <v>257</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>482</v>
+        <v>420</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>80</v>
+        <v>421</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>483</v>
+        <v>422</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>483</v>
+        <v>422</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14164,7 +14100,7 @@
         <v>88</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>80</v>
@@ -14173,16 +14109,16 @@
         <v>80</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>484</v>
+        <v>423</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>485</v>
+        <v>424</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>486</v>
+        <v>425</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14232,7 +14168,7 @@
         <v>80</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>483</v>
+        <v>422</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -14247,24 +14183,24 @@
         <v>100</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>80</v>
+        <v>426</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>487</v>
+        <v>427</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>80</v>
+        <v>428</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>80</v>
+        <v>429</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>488</v>
+        <v>430</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>488</v>
+        <v>430</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14287,15 +14223,17 @@
         <v>80</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>171</v>
+        <v>431</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>172</v>
+        <v>432</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N107" s="2"/>
+        <v>433</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>80</v>
@@ -14344,7 +14282,7 @@
         <v>80</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>174</v>
+        <v>430</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -14356,31 +14294,31 @@
         <v>80</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>80</v>
+        <v>426</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>169</v>
+        <v>435</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>80</v>
+        <v>436</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>489</v>
+        <v>437</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>489</v>
+        <v>437</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>133</v>
+        <v>438</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -14396,19 +14334,19 @@
         <v>80</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>134</v>
+        <v>212</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>135</v>
+        <v>439</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>176</v>
+        <v>440</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>137</v>
+        <v>441</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -14434,13 +14372,13 @@
         <v>80</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>80</v>
+        <v>442</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>80</v>
+        <v>443</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>80</v>
@@ -14458,7 +14396,7 @@
         <v>80</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>177</v>
+        <v>437</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -14470,31 +14408,31 @@
         <v>80</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>80</v>
+        <v>444</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>169</v>
+        <v>445</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>80</v>
+        <v>446</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>80</v>
+        <v>447</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>490</v>
+        <v>448</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>490</v>
+        <v>448</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>179</v>
+        <v>438</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -14507,26 +14445,24 @@
         <v>80</v>
       </c>
       <c r="I109" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J109" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>134</v>
+        <v>449</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>180</v>
+        <v>450</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>181</v>
+        <v>440</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>80</v>
       </c>
@@ -14574,7 +14510,7 @@
         <v>80</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>182</v>
+        <v>448</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -14586,27 +14522,27 @@
         <v>80</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>80</v>
+        <v>444</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>131</v>
+        <v>445</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>80</v>
+        <v>446</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>80</v>
+        <v>447</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>491</v>
+        <v>451</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>491</v>
+        <v>451</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14617,7 +14553,7 @@
         <v>78</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>80</v>
@@ -14626,16 +14562,16 @@
         <v>80</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>492</v>
+        <v>452</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>493</v>
+        <v>453</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -14686,13 +14622,13 @@
         <v>80</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>491</v>
+        <v>451</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>80</v>
@@ -14704,21 +14640,21 @@
         <v>80</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>150</v>
+        <v>454</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>494</v>
+        <v>80</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>495</v>
+        <v>455</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>495</v>
+        <v>455</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14741,13 +14677,13 @@
         <v>80</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>496</v>
+        <v>171</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>497</v>
+        <v>172</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>498</v>
+        <v>173</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -14798,7 +14734,7 @@
         <v>80</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>495</v>
+        <v>174</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -14810,13 +14746,13 @@
         <v>80</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>499</v>
+        <v>169</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>80</v>
@@ -14827,21 +14763,21 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>500</v>
+        <v>456</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>500</v>
+        <v>456</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>80</v>
@@ -14853,15 +14789,17 @@
         <v>80</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>212</v>
+        <v>134</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>501</v>
+        <v>135</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N112" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>80</v>
@@ -14886,13 +14824,13 @@
         <v>80</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>503</v>
+        <v>80</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>504</v>
+        <v>80</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>80</v>
@@ -14910,71 +14848,75 @@
         <v>80</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>500</v>
+        <v>177</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>505</v>
+        <v>169</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>506</v>
+        <v>80</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>507</v>
+        <v>457</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>507</v>
+        <v>457</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I113" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>212</v>
+        <v>134</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>508</v>
+        <v>180</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="N113" s="2"/>
-      <c r="O113" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P113" t="s" s="2">
         <v>80</v>
       </c>
@@ -14998,13 +14940,13 @@
         <v>80</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>216</v>
+        <v>80</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>510</v>
+        <v>80</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>511</v>
+        <v>80</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>80</v>
@@ -15022,50 +14964,50 @@
         <v>80</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>507</v>
+        <v>182</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>512</v>
+        <v>80</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>513</v>
+        <v>458</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>513</v>
+        <v>458</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>80</v>
+        <v>459</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>80</v>
@@ -15074,23 +15016,21 @@
         <v>80</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>212</v>
+        <v>460</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>514</v>
+        <v>461</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>515</v>
+        <v>462</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>517</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>80</v>
       </c>
@@ -15114,13 +15054,13 @@
         <v>80</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>216</v>
+        <v>80</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>518</v>
+        <v>80</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>519</v>
+        <v>80</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>80</v>
@@ -15138,13 +15078,13 @@
         <v>80</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>513</v>
+        <v>458</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>80</v>
@@ -15153,24 +15093,24 @@
         <v>100</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>80</v>
+        <v>463</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>520</v>
+        <v>464</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>80</v>
+        <v>446</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>521</v>
+        <v>465</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>522</v>
+        <v>466</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>522</v>
+        <v>466</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15181,7 +15121,7 @@
         <v>78</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>80</v>
@@ -15196,10 +15136,10 @@
         <v>212</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>523</v>
+        <v>467</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>524</v>
+        <v>468</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -15229,10 +15169,10 @@
         <v>112</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>525</v>
+        <v>469</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>526</v>
+        <v>470</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>80</v>
@@ -15250,13 +15190,13 @@
         <v>80</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>522</v>
+        <v>466</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>80</v>
@@ -15268,21 +15208,21 @@
         <v>80</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>527</v>
+        <v>169</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>528</v>
+        <v>80</v>
       </c>
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>529</v>
+        <v>471</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>529</v>
+        <v>471</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15293,7 +15233,7 @@
         <v>78</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>80</v>
@@ -15305,13 +15245,13 @@
         <v>80</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>212</v>
+        <v>472</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>530</v>
+        <v>473</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>531</v>
+        <v>474</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -15338,13 +15278,13 @@
         <v>80</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>532</v>
+        <v>80</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>533</v>
+        <v>80</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>80</v>
@@ -15362,13 +15302,13 @@
         <v>80</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>529</v>
+        <v>471</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>80</v>
@@ -15380,21 +15320,21 @@
         <v>80</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>534</v>
+        <v>475</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>535</v>
+        <v>80</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>536</v>
+        <v>476</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>536</v>
+        <v>476</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15405,7 +15345,7 @@
         <v>78</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>80</v>
@@ -15417,15 +15357,17 @@
         <v>80</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>496</v>
+        <v>477</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>537</v>
+        <v>478</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="N117" s="2"/>
+        <v>479</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>480</v>
+      </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>80</v>
@@ -15474,13 +15416,13 @@
         <v>80</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>536</v>
+        <v>476</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>80</v>
@@ -15492,21 +15434,21 @@
         <v>80</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>539</v>
+        <v>481</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>540</v>
+        <v>80</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>541</v>
+        <v>482</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>541</v>
+        <v>482</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15529,15 +15471,17 @@
         <v>80</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>212</v>
+        <v>165</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>542</v>
+        <v>483</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="N118" s="2"/>
+        <v>484</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>485</v>
+      </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>80</v>
@@ -15562,13 +15506,13 @@
         <v>80</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>216</v>
+        <v>80</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>544</v>
+        <v>80</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>545</v>
+        <v>80</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>80</v>
@@ -15586,7 +15530,7 @@
         <v>80</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>541</v>
+        <v>482</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -15604,21 +15548,21 @@
         <v>80</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>546</v>
+        <v>486</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>547</v>
+        <v>80</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>548</v>
+        <v>487</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>548</v>
+        <v>487</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15632,7 +15576,7 @@
         <v>88</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>80</v>
@@ -15641,17 +15585,15 @@
         <v>80</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>549</v>
+        <v>172</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>551</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>80</v>
@@ -15700,25 +15642,25 @@
         <v>80</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>548</v>
+        <v>174</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>552</v>
+        <v>169</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>80</v>
@@ -15729,21 +15671,21 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>553</v>
+        <v>488</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>553</v>
+        <v>488</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>80</v>
@@ -15755,15 +15697,17 @@
         <v>80</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N120" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>80</v>
@@ -15812,19 +15756,19 @@
         <v>80</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AK120" t="s" s="2">
         <v>80</v>
@@ -15841,14 +15785,14 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>554</v>
+        <v>489</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>554</v>
+        <v>489</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
@@ -15861,24 +15805,26 @@
         <v>80</v>
       </c>
       <c r="I121" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K121" t="s" s="2">
         <v>134</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="N121" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="O121" s="2"/>
+      <c r="O121" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P121" t="s" s="2">
         <v>80</v>
       </c>
@@ -15926,7 +15872,7 @@
         <v>80</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -15944,7 +15890,7 @@
         <v>80</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>80</v>
@@ -15955,46 +15901,42 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>555</v>
+        <v>490</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>555</v>
+        <v>490</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I122" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J122" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>180</v>
+        <v>491</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>492</v>
+      </c>
+      <c r="N122" s="2"/>
+      <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>80</v>
       </c>
@@ -16042,39 +15984,39 @@
         <v>80</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>182</v>
+        <v>490</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>80</v>
+        <v>493</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>556</v>
+        <v>494</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>556</v>
+        <v>494</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16082,7 +16024,7 @@
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G123" t="s" s="2">
         <v>88</v>
@@ -16097,13 +16039,13 @@
         <v>80</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>557</v>
+        <v>495</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>558</v>
+        <v>496</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>559</v>
+        <v>497</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -16154,10 +16096,10 @@
         <v>80</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>556</v>
+        <v>494</v>
       </c>
       <c r="AG123" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH123" t="s" s="2">
         <v>88</v>
@@ -16169,24 +16111,24 @@
         <v>100</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>560</v>
+        <v>80</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>288</v>
+        <v>498</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>561</v>
+        <v>80</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>562</v>
+        <v>80</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>563</v>
+        <v>499</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>563</v>
+        <v>499</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16209,17 +16151,15 @@
         <v>80</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>108</v>
+        <v>212</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>564</v>
+        <v>500</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>566</v>
-      </c>
+        <v>501</v>
+      </c>
+      <c r="N124" s="2"/>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>80</v>
@@ -16244,13 +16184,13 @@
         <v>80</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>157</v>
+        <v>112</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>567</v>
+        <v>502</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>568</v>
+        <v>503</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>80</v>
@@ -16268,7 +16208,7 @@
         <v>80</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>563</v>
+        <v>499</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -16286,21 +16226,21 @@
         <v>80</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>569</v>
+        <v>504</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>80</v>
+        <v>505</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>570</v>
+        <v>506</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>570</v>
+        <v>506</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16326,14 +16266,12 @@
         <v>212</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>571</v>
+        <v>507</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>573</v>
-      </c>
+        <v>508</v>
+      </c>
+      <c r="N125" s="2"/>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>80</v>
@@ -16361,10 +16299,10 @@
         <v>216</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>574</v>
+        <v>509</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>575</v>
+        <v>510</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>80</v>
@@ -16382,7 +16320,7 @@
         <v>80</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>570</v>
+        <v>506</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -16400,21 +16338,21 @@
         <v>80</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>80</v>
+        <v>169</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>80</v>
+        <v>511</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>576</v>
+        <v>512</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>576</v>
+        <v>512</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16425,7 +16363,7 @@
         <v>78</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>80</v>
@@ -16437,16 +16375,20 @@
         <v>80</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>186</v>
+        <v>212</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>577</v>
+        <v>513</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="N126" s="2"/>
-      <c r="O126" s="2"/>
+        <v>514</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>516</v>
+      </c>
       <c r="P126" t="s" s="2">
         <v>80</v>
       </c>
@@ -16470,13 +16412,13 @@
         <v>80</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>80</v>
+        <v>216</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>80</v>
+        <v>517</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>80</v>
+        <v>518</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>80</v>
@@ -16494,13 +16436,13 @@
         <v>80</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>576</v>
+        <v>512</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>80</v>
@@ -16512,21 +16454,21 @@
         <v>80</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>281</v>
+        <v>519</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>80</v>
+        <v>520</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>579</v>
+        <v>521</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>579</v>
+        <v>521</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16537,7 +16479,7 @@
         <v>78</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>80</v>
@@ -16549,13 +16491,13 @@
         <v>80</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>580</v>
+        <v>212</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>581</v>
+        <v>522</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>582</v>
+        <v>523</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -16582,13 +16524,13 @@
         <v>80</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>80</v>
+        <v>524</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>80</v>
+        <v>525</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>80</v>
@@ -16606,13 +16548,13 @@
         <v>80</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>579</v>
+        <v>521</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>80</v>
@@ -16621,24 +16563,24 @@
         <v>100</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>287</v>
+        <v>80</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>583</v>
+        <v>526</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>584</v>
+        <v>527</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>585</v>
+        <v>528</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>585</v>
+        <v>528</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16649,7 +16591,7 @@
         <v>78</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>80</v>
@@ -16661,17 +16603,15 @@
         <v>80</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>586</v>
+        <v>212</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>587</v>
+        <v>529</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>589</v>
-      </c>
+        <v>530</v>
+      </c>
+      <c r="N128" s="2"/>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>80</v>
@@ -16696,13 +16636,13 @@
         <v>80</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>80</v>
+        <v>531</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>80</v>
+        <v>532</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>80</v>
@@ -16720,13 +16660,13 @@
         <v>80</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>585</v>
+        <v>528</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>80</v>
@@ -16735,20 +16675,1378 @@
         <v>100</v>
       </c>
       <c r="AK128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL128" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AM128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN128" t="s" s="2">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="129" hidden="true">
+      <c r="A129" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E129" s="2"/>
+      <c r="F129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="N129" s="2"/>
+      <c r="O129" s="2"/>
+      <c r="P129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q129" s="2"/>
+      <c r="R129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL129" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AM129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN129" t="s" s="2">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="130" hidden="true">
+      <c r="A130" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="N130" s="2"/>
+      <c r="O130" s="2"/>
+      <c r="P130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q130" s="2"/>
+      <c r="R130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL130" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AM130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN130" t="s" s="2">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="131" hidden="true">
+      <c r="A131" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="O131" s="2"/>
+      <c r="P131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL131" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AM131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN131" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="132" hidden="true">
+      <c r="A132" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E132" s="2"/>
+      <c r="F132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="N132" s="2"/>
+      <c r="O132" s="2"/>
+      <c r="P132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q132" s="2"/>
+      <c r="R132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL132" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AM132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN132" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="133" hidden="true">
+      <c r="A133" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E133" s="2"/>
+      <c r="F133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O133" s="2"/>
+      <c r="P133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL133" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AM133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN133" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="134" hidden="true">
+      <c r="A134" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="E134" s="2"/>
+      <c r="F134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O134" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="P134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q134" s="2"/>
+      <c r="R134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL134" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AM134" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN134" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="135" hidden="true">
+      <c r="A135" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E135" s="2"/>
+      <c r="F135" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G135" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K135" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="N135" s="2"/>
+      <c r="O135" s="2"/>
+      <c r="P135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q135" s="2"/>
+      <c r="R135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF135" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AG135" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH135" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ135" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK135" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AL135" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AM135" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AN135" t="s" s="2">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="136" hidden="true">
+      <c r="A136" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="C136" s="2"/>
+      <c r="D136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E136" s="2"/>
+      <c r="F136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G136" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K136" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="N136" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="O136" s="2"/>
+      <c r="P136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q136" s="2"/>
+      <c r="R136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X136" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="Z136" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AA136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF136" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AG136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH136" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ136" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL136" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AM136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN136" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="137" hidden="true">
+      <c r="A137" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="D137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E137" s="2"/>
+      <c r="F137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G137" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K137" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L137" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="M137" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="O137" s="2"/>
+      <c r="P137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q137" s="2"/>
+      <c r="R137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X137" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="Z137" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AA137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF137" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AG137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH137" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ137" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN137" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="138" hidden="true">
+      <c r="A138" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="C138" s="2"/>
+      <c r="D138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E138" s="2"/>
+      <c r="F138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G138" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K138" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M138" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="N138" s="2"/>
+      <c r="O138" s="2"/>
+      <c r="P138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q138" s="2"/>
+      <c r="R138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF138" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AG138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH138" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ138" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL138" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AM138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN138" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="139" hidden="true">
+      <c r="A139" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="C139" s="2"/>
+      <c r="D139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E139" s="2"/>
+      <c r="F139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G139" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K139" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="L139" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="M139" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="N139" s="2"/>
+      <c r="O139" s="2"/>
+      <c r="P139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q139" s="2"/>
+      <c r="R139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF139" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AG139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH139" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ139" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK139" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AL139" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AM139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN139" t="s" s="2">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="140" hidden="true">
+      <c r="A140" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="C140" s="2"/>
+      <c r="D140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E140" s="2"/>
+      <c r="F140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G140" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K140" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="L140" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="M140" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="O140" s="2"/>
+      <c r="P140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q140" s="2"/>
+      <c r="R140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF140" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AG140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH140" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ140" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK140" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AL140" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="AL128" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="AM128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN128" t="s" s="2">
+      <c r="AM140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN140" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN128">
+  <autoFilter ref="A1:AN140">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16758,7 +18056,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI127">
+  <conditionalFormatting sqref="A2:AI139">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-encounter.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-encounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
